--- a/mark59-datahunter-samples/mark59serverprofiles.xlsx
+++ b/mark59-datahunter-samples/mark59serverprofiles.xlsx
@@ -81,7 +81,7 @@
     <t>DemoLINUX-DataHunterSeleniumRunCheck</t>
   </si>
   <si>
-    <t>Loads Trend Analysis (H2 database).  See:&lt;br&gt;http://localhost:8083/metrics/trending?reqApp=DataHunter</t>
+    <t>Loads Trend Analysis (H2 database).  See:&lt;br&gt;http://localhost:8083/mark59-trends/trending?reqApp=DataHunter</t>
   </si>
   <si>
     <t>DemoWIN-DataHunterSeleniumDeployAndExecute</t>
@@ -220,23 +220,23 @@
  echo Running Directly From Server Metrics Web (cmd DataHunterSeleniumDeployAndExecute) &amp; 
  echo  SERVER_METRICS_WEB_BASE_DIR: %SERVER_METRICS_WEB_BASE_DIR% &amp; 
  cd /D %SERVER_METRICS_WEB_BASE_DIR% &amp;  
- cd ..\dataHunterPerformanceTestSamples &amp; 
+ cd ..\mark59-datahunter-samples &amp; 
  DEL C:\apache-jmeter\bin\mark59.properties &amp; COPY .\mark59.properties C:\apache-jmeter\bin &amp;
  DEL C:\apache-jmeter\bin\chromedriver.exe  &amp; COPY .\chromedriver.exe  C:\apache-jmeter\bin &amp;
- DEL C:\apache-jmeter\lib\ext\mark59-server-metrics.jar &amp;
- COPY ..\mark59-server-metrics\target\mark59-server-metrics.jar  C:\apache-jmeter\lib\ext &amp; 
- DEL C:\apache-jmeter\lib\ext\dataHunterPerformanceTestSamples.jar &amp; 
- COPY .\target\dataHunterPerformanceTestSamples.jar  C:\apache-jmeter\lib\ext &amp;
- RMDIR /S /Q C:\apache-jmeter\lib\ext\dataHunterPerformanceTestSamples-dependencies &amp;
- MKDIR C:\apache-jmeter\lib\ext\dataHunterPerformanceTestSamples-dependencies &amp;
- COPY .\target\dataHunterPerformanceTestSamples-dependencies  C:\apache-jmeter\lib\ext\dataHunterPerformanceTestSamples-dependencies &amp;
+ DEL C:\apache-jmeter\lib\ext\mark59-metrics.jar &amp;
+ COPY ..\mark59-metrics\target\mark59-metrics.jar  C:\apache-jmeter\lib\ext &amp; 
+ DEL C:\apache-jmeter\lib\ext\mark59-datahunter-samples.jar &amp; 
+ COPY .\target\mark59-datahunter-samples.jar  C:\apache-jmeter\lib\ext &amp;
+ RMDIR /S /Q C:\apache-jmeter\lib\ext\mark59-datahunter-samples-dependencies &amp;
+ MKDIR C:\apache-jmeter\lib\ext\mark59-datahunter-samples-dependencies &amp;
+ COPY .\target\mark59-datahunter-samples-dependencies  C:\apache-jmeter\lib\ext\mark59-datahunter-samples-dependencies &amp;
  mkdir C:\Mark59_Runs &amp;
  mkdir C:\Mark59_Runs\Jmeter_Results &amp;
  mkdir C:\Mark59_Runs\Jmeter_Results\DataHunter &amp;
  set path=%path%;C:\Windows\System32;C:\windows\system32\wbem &amp; 
  cd /D C:\apache-jmeter\bin &amp;
  echo Starting JMeter DataHunter test ... &amp;  
- jmeter -n -X -f -t %SERVER_METRICS_WEB_BASE_DIR%\..\dataHunterPerformanceTestSamples\test-plans\DataHunterSeleniumTestPlan.jmx -l C:\Mark59_Runs\Jmeter_Results\DataHunter\DataHunterTestResults.csv -JForceTxnFailPercent=0 -JDataHunterUrl=http://localhost:8081/dataHunter -JStartCdpListeners=false &amp;
+ jmeter -n -X -f -t %SERVER_METRICS_WEB_BASE_DIR%\..\mark59-datahunter-samples\test-plans\DataHunterSeleniumTestPlan.jmx -l C:\Mark59_Runs\Jmeter_Results\DataHunter\DataHunterTestResults.csv -JForceTxnFailPercent=0 -JDataHunterUrl=http://localhost:8081/mark59-datahunter -JStartCdpListeners=false &amp;
  PAUSE
 '
 </t>
@@ -245,7 +245,7 @@
     <t>N</t>
   </si>
   <si>
-    <t xml:space="preserve">refer DeployDataHunterTestArtifactsToJmeter.bat and DataHunterExecuteJmeterTest.bat in dataHunterPerformanceTestSamples </t>
+    <t xml:space="preserve">refer DeployDataHunterTestArtifactsToJmeter.bat and DataHunterExecuteJmeterTest.bat in mark59-datahunter-samples </t>
   </si>
   <si>
     <t>[]</t>
@@ -254,16 +254,16 @@
     <t>echo This script runs the JMeter deploy in the background, then opens a terminal for JMeter execution.
 echo starting from $PWD;
 {   # try  
-    cd ../dataHunterPerformanceTestSamples &amp;&amp; 
+    cd ../mark59-datahunter-samples &amp;&amp; 
     DH_TEST_SAMPLES_DIR=$(pwd) &amp;&amp; 
-    echo dataHunterPerformanceTestSamples base dir is $DH_TEST_SAMPLES_DIR &amp;&amp;
+    echo mark59-datahunter-samples base dir is $DH_TEST_SAMPLES_DIR &amp;&amp;
     cp ./mark59.properties ~/apache-jmeter/bin/mark59.properties &amp;&amp;
     cp ./chromedriver ~/apache-jmeter/bin/chromedriver &amp;&amp; 
-    cp ../mark59-server-metrics/target/mark59-server-metrics.jar  ~/apache-jmeter/lib/ext/mark59-server-metrics.jar &amp;&amp; 
-    cp ./target/dataHunterPerformanceTestSamples.jar  ~/apache-jmeter/lib/ext/dataHunterPerformanceTestSamples.jar &amp;&amp; 
+    cp ../mark59-metrics/target/mark59-metrics.jar  ~/apache-jmeter/lib/ext/mark59-metrics.jar &amp;&amp; 
+    cp ./target/mark59-datahunter-samples.jar  ~/apache-jmeter/lib/ext/mark59-datahunter-samples.jar &amp;&amp; 
     mkdir -p ~/Mark59_Runs/Jmeter_Results/DataHunter &amp;&amp;
-    rm -rf ~/apache-jmeter/lib/ext/dataHunterPerformanceTestSamples-dependencies &amp;&amp;
-    cp -r ./target/dataHunterPerformanceTestSamples-dependencies ~/apache-jmeter/lib/ext/dataHunterPerformanceTestSamples-dependencies &amp;&amp;
+    rm -rf ~/apache-jmeter/lib/ext/mark59-datahunter-samples-dependencies &amp;&amp;
+    cp -r ./target/mark59-datahunter-samples-dependencies ~/apache-jmeter/lib/ext/mark59-datahunter-samples-dependencies &amp;&amp;
     gnome-terminal -- sh -c "~/apache-jmeter/bin/jmeter -n -X -f -t $DH_TEST_SAMPLES_DIR/test-plans/DataHunterSeleniumTestPlan.jmx -l ~/Mark59_Runs/Jmeter_Results/DataHunter/DataHunterTestResults.csv -JForceTxnFailPercent=0 -JStartCdpListeners=false; exec bash"
 } || { # catch 
     echo Deploy was unsuccessful! 
@@ -298,22 +298,22 @@
   </si>
   <si>
     <t xml:space="preserve">process call create 'cmd.exe /c 
- echo Load DataHunter Test Results into  Mark59 Metrics (Trend Analysis) h2 database. &amp; 
+ echo Load DataHunter Test Results into  Mark59 Trends Analysis h2 database. &amp; 
  cd /D  %SERVER_METRICS_WEB_BASE_DIR% &amp; 
- cd ../metricsRuncheck &amp;  
- java -jar ./target/metricsRuncheck.jar -a DataHunter -i C:\Mark59_Runs\Jmeter_Results\DataHunter -d h2 &amp;
+ cd ../mark59-trends-load &amp;  
+ java -jar ./target/mark59-trends-load.jar -a DataHunter -i C:\Mark59_Runs\Jmeter_Results\DataHunter -d h2 &amp;
  PAUSE
 '
 </t>
   </si>
   <si>
-    <t xml:space="preserve">echo This script runs metricsRuncheck,to load results from a DataHunter test run into the Metrics Trend Analysis Graph.
+    <t xml:space="preserve">echo This script runs mark59-trends-load,to load results from a DataHunter test run into the Metrics Trend Analysis Graph.
 echo starting from $PWD;
 {   # try  
-    cd ../metricsRuncheck/target &amp;&amp;
-    gnome-terminal -- sh -c "java -jar metricsRuncheck.jar -a DataHunter -i ~/Mark59_Runs/Jmeter_Results/DataHunter -d h2; exec bash"
+    cd ../mark59-trends-load/target &amp;&amp;
+    gnome-terminal -- sh -c "java -jar mark59-trends-load.jar -a DataHunter -i ~/Mark59_Runs/Jmeter_Results/DataHunter -d h2; exec bash"
 } || { # catch 
-    echo attempt to execute metricsRuncheck has failed! 
+    echo attempt to execute mark59-trends-load has failed! 
 }
 </t>
   </si>
@@ -802,7 +802,7 @@
     <col min="7" max="7" width="19.46484375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="19.5390625" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="23.23828125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="102.359375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="103.01953125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="71.546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1523,7 +1523,7 @@
     <col min="2" max="2" width="17.41015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="255.0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="16.45703125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="117.37890625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="109.81640625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="62.10546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/mark59-datahunter-samples/mark59serverprofiles.xlsx
+++ b/mark59-datahunter-samples/mark59serverprofiles.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Reports generated at   ~/Mark59_Runs/Jmeter_Reports/DataHunter/   &lt;br&gt;(open each index.html)   </t>
   </si>
   <si>
-    <t>DemoLINUX-DataHunterSeleniumRunCheck</t>
+    <t>DemoLINUX-DataHunterSeleniumTrendsLoad</t>
   </si>
   <si>
     <t>Loads Trend Analysis (H2 database).  See:&lt;br&gt;http://localhost:8083/mark59-trends/trending?reqApp=DataHunter</t>
@@ -96,7 +96,7 @@
     <t>Hint - in browser open this URL and go to each index.html:  file:///C:/Mark59_Runs/Jmeter_Reports/DataHunter/</t>
   </si>
   <si>
-    <t>DemoWIN-DataHunterSeleniumRunCheck</t>
+    <t>DemoWIN-DataHunterSeleniumTrendsLoad</t>
   </si>
   <si>
     <t>NewRelicTestProfile</t>
@@ -168,7 +168,7 @@
     <t>DataHunterSeleniumGenJmeterReport_LINUX</t>
   </si>
   <si>
-    <t>DataHunterSeleniumRunCheck_LINUX</t>
+    <t>DataHunterSeleniumTrendsLoad_LINUX</t>
   </si>
   <si>
     <t>DataHunterSeleniumDeployAndExecute</t>
@@ -177,7 +177,7 @@
     <t>DataHunterSeleniumGenJmeterReport</t>
   </si>
   <si>
-    <t>DataHunterSeleniumRunCheck</t>
+    <t>DataHunterSeleniumTrendsLoad</t>
   </si>
   <si>
     <t>NewRelicSampleCmd</t>
@@ -223,8 +223,8 @@
  cd ..\mark59-datahunter-samples &amp; 
  DEL C:\apache-jmeter\bin\mark59.properties &amp; COPY .\mark59.properties C:\apache-jmeter\bin &amp;
  DEL C:\apache-jmeter\bin\chromedriver.exe  &amp; COPY .\chromedriver.exe  C:\apache-jmeter\bin &amp;
- DEL C:\apache-jmeter\lib\ext\mark59-metrics.jar &amp;
- COPY ..\mark59-metrics\target\mark59-metrics.jar  C:\apache-jmeter\lib\ext &amp; 
+ DEL C:\apache-jmeter\lib\ext\mark59-metrics-api.jar &amp;
+ COPY ..\mark59-metrics-api\target\mark59-metrics-api.jar  C:\apache-jmeter\lib\ext &amp; 
  DEL C:\apache-jmeter\lib\ext\mark59-datahunter-samples.jar &amp; 
  COPY .\target\mark59-datahunter-samples.jar  C:\apache-jmeter\lib\ext &amp;
  RMDIR /S /Q C:\apache-jmeter\lib\ext\mark59-datahunter-samples-dependencies &amp;
@@ -259,7 +259,7 @@
     echo mark59-datahunter-samples base dir is $DH_TEST_SAMPLES_DIR &amp;&amp;
     cp ./mark59.properties ~/apache-jmeter/bin/mark59.properties &amp;&amp;
     cp ./chromedriver ~/apache-jmeter/bin/chromedriver &amp;&amp; 
-    cp ../mark59-metrics/target/mark59-metrics.jar  ~/apache-jmeter/lib/ext/mark59-metrics.jar &amp;&amp; 
+    cp ../mark59-metrics-api/target/mark59-metrics-api.jar  ~/apache-jmeter/lib/ext/mark59-metrics-api.jar &amp;&amp; 
     cp ./target/mark59-datahunter-samples.jar  ~/apache-jmeter/lib/ext/mark59-datahunter-samples.jar &amp;&amp; 
     mkdir -p ~/Mark59_Runs/Jmeter_Results/DataHunter &amp;&amp;
     rm -rf ~/apache-jmeter/lib/ext/mark59-datahunter-samples-dependencies &amp;&amp;
@@ -278,7 +278,7 @@
   <si>
     <t xml:space="preserve">process call create 'cmd.exe /c 
  cd /D %SERVER_METRICS_WEB_BASE_DIR% &amp; 
- cd../resultFilesConverter &amp; 
+ cd../mark59-results-splitter &amp; 
  CreateDataHunterJmeterReports.bat'
 </t>
   </si>
@@ -286,7 +286,7 @@
     <t xml:space="preserve">echo This script creates a set of JMeter reports from a DataHunter test run.
 echo starting from $PWD;
 {   # try  
-    cd ../resultFilesConverter
+    cd ../mark59-results-splitter
     gnome-terminal -- sh -c "./CreateDataHunterJmeterReports.sh; exec bash"
 } || { # catch 
     echo attempt to generate JMeter Reports has failed! 
@@ -318,7 +318,7 @@
 </t>
   </si>
   <si>
-    <t>refer bin/TestRunLINUX-DataHunter-Selenium-metricsRunCheck.sh</t>
+    <t>refer bin/TestRunLINUX-DataHunter-Selenium-metricsTrendsLoad.sh</t>
   </si>
   <si>
     <t>OS get FreePhysicalMemory</t>
@@ -349,8 +349,8 @@
 import org.apache.commons.lang3.StringUtils;
 import org.json.JSONArray;
 import org.json.JSONObject;
-import com.mark59.servermetricsweb.pojos.ParsedMetric;
-import com.mark59.servermetricsweb.pojos.ScriptResponse;
+import com.mark59.metrics.pojos.ParsedMetric;
+import com.mark59.metrics.pojos.ScriptResponse;
 ScriptResponse scriptResponse = new ScriptResponse(); 
 List&lt;ParsedMetric&gt; parsedMetrics = new ArrayList&lt;ParsedMetric&gt;();
 String newRelicApiUrl = "https://api.newrelic.com/v2/applications/";
@@ -424,9 +424,9 @@
   <si>
     <t>import java.util.ArrayList;
 import java.util.List;
-import com.mark59.servermetricsweb.data.beans.ServerProfile;
-import com.mark59.servermetricsweb.pojos.ParsedMetric;
-import com.mark59.servermetricsweb.pojos.ScriptResponse;
+import com.mark59.metrics.data.beans.ServerProfile;
+import com.mark59.metrics.pojos.ParsedMetric;
+import com.mark59.metrics.pojos.ScriptResponse;
 ScriptResponse scriptResponse = new ScriptResponse();
 List&lt;ParsedMetric&gt; parsedMetrics = new ArrayList&lt;ParsedMetric&gt;();
 String commandLogDebug = "running script " + serverProfile.getServerProfileName() + "&lt;br&gt;" +  serverProfile.getComment();
